--- a/강아지 입양 여부- 답지.xlsx
+++ b/강아지 입양 여부- 답지.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="53">
   <si>
     <t xml:space="preserve">아래의 표는 각각의 조건이 주어졌을 때 강아지 입양 여부 테이블 입니다. </t>
   </si>
@@ -120,52 +120,64 @@
     <t xml:space="preserve">답                 :</t>
   </si>
   <si>
+    <t xml:space="preserve">X =(주거지 = 김해, 수입 = medium, 성별 = 남자, 신용등급=excellent) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. 위의 테이블을 참고하여 각각의 주어진 확률 값을 구하시오 단 소수점 셋째 자리까지 구하시오. (COUNTIF문, ROUND함수 사용)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(강아지 입양 여부=yes) &lt; 모든 사람들 중에서 얼마나 많은 비율이 강아지를 입양하였는지를 나타냄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(강아지 입양 여부 = no) &lt;- 모든 사람들 중에서 얼마나 많은 비율이 강아지를 입양하지 않았는지를 나타냄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(주거지=김해 | 강아지 입양 여부=yes) &lt;-강아지를 입양한 사람들 중에서 주거지가 '김해'인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(주거지=김해 | 강아지 입양 여부=no) &lt;-강아지를 입양하지 않은 사람들 중에서 주거지가 김해인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(수입=medium | 강아지 입양 여부=yes) &lt;-강아지를 입양한 사람들 중에서 수입이 medium인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(수입=medium |강아지 입양 여부=no) &lt;-강아지를 입양하지 않은 사람들 중에서 수입이 medium인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(성별=남자 | 강아지 입양 여부=yes)&lt;-강아지를 입양한 사람들 중에서 성별이 남자인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(성별=남자 | 강아지 입양 여부=no)&lt;-강아지를 입양 하지 않은 사람들 중에서 성별이 남자인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(신용등급=excellent | 강아지 입양 여부=yes)&lt;-강아지를 입양한 사람들 중에서 신용등급이 excellent인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P(신용등급=excellent | 강아지 입양 여부=no)&lt;-강아지를 입양 하지 않은 사람들 중에서 신용등급이 excellent인 사람의 비율</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. 아래와 같이 X라는 사람의 조건이 주어졌을 때 P(X|강아지 입양 여부 = yes, no)인 확률을 구하시오(위에 확률들 참고해서 작성)</t>
+  </si>
+  <si>
     <t xml:space="preserve">X =(주거지 = 김해, 수입 = medium, 성별 = 남자, 신용등급=fair) </t>
   </si>
   <si>
-    <t xml:space="preserve">4. 위의 테이블을 참고하여 각각의 주어진 확률 값을 구하시오 단 소수점 셋째 자리까지 구하시오. (COUNTIF문, ROUND함수 사용)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(강아지 입양 여부=yes) &lt; 모든 사람들 중에서 얼마나 많은 비율이 강아지를 입양하였는지를 나타냄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(강아지 입양 여부 = no) &lt;- 모든 사람들 중에서 얼마나 많은 비율이 강아지를 입양하지 않았는지를 나타냄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(주거지=김해 | 강아지 입양 여부=yes) &lt;-강아지를 입양한 사람들 중에서 주거지가 '김해'인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(주거지=김해 | 강아지 입양 여부=no) &lt;-강아지를 입양하지 않은 사람들 중에서 주거지가 김해인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(수입=medium | 강아지 입양 여부=yes) &lt;-강아지를 입양한 사람들 중에서 수입이 medium인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(수입=medium |강아지 입양 여부=no) &lt;-강아지를 입양하지 않은 사람들 중에서 수입이 medium인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(성별=남자 | 강아지 입양 여부=yes)&lt;-강아지를 입양한 사람들 중에서 성별이 남자인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(성별=남자 | 강아지 입양 여부=no)&lt;-강아지를 입양 하지 않은 사람들 중에서 성별이 남자인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(신용등급=fair | 강아지 입양 여부=yes)&lt;-강아지를 입양한 사람들 중에서 신용등급이 fair인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P(신용등급=fair | 강아지 입양 여부=no)&lt;-강아지를 입양 하지 않은 사람들 중에서 신용등급이 fair인 사람의 비율</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. 아래와 같이 X라는 사람의 조건이 주어졌을 때 P(X|강아지 입양 여부 = yes, no)인 확률을 구하시오(위에 확률들 참고해서 작성)</t>
-  </si>
-  <si>
     <t xml:space="preserve">답  (yes)         :       </t>
   </si>
   <si>
     <t xml:space="preserve">답  (no)          :       </t>
   </si>
   <si>
-    <t xml:space="preserve">6. 5번에서 두 확률을 비교하고 큰 값을 적으시오</t>
+    <t xml:space="preserve">6. (1)P(X|강아지 입양 여부=yes) * P(강아지 입양 여부 = yes),  (2)P(X|강아지 입양 여부=no) * P(강아지 입양 여부 = no) 의 확률을 구하시오</t>
+  </si>
+  <si>
+    <t xml:space="preserve">답  (1)           :       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">답  (2)           :       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. 6번에서 두 확률을 비교하고 큰 값을 적으시오</t>
   </si>
   <si>
     <t xml:space="preserve">답                 :       </t>
@@ -468,7 +480,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AS91"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.5"/>
@@ -481,10 +493,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -497,7 +509,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -517,7 +529,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
         <v>1</v>
       </c>
@@ -537,7 +549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,7 +569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>3</v>
       </c>
@@ -577,7 +589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,7 +609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>5</v>
       </c>
@@ -617,7 +629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>6</v>
       </c>
@@ -640,7 +652,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>7</v>
       </c>
@@ -660,7 +672,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>8</v>
       </c>
@@ -680,7 +692,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>9</v>
       </c>
@@ -700,7 +712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>10</v>
       </c>
@@ -720,7 +732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>11</v>
       </c>
@@ -740,7 +752,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>12</v>
       </c>
@@ -760,7 +772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>13</v>
       </c>
@@ -780,7 +792,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>14</v>
       </c>
@@ -800,14 +812,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="9"/>
       <c r="K19" s="9"/>
     </row>
-    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -816,7 +828,7 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
         <v>25</v>
       </c>
@@ -825,7 +837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -834,7 +846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
         <v>27</v>
       </c>
@@ -844,7 +856,7 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
@@ -853,7 +865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
         <v>29</v>
       </c>
@@ -862,7 +874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
         <v>30</v>
       </c>
@@ -873,7 +885,7 @@
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
     </row>
-    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
         <v>31</v>
       </c>
@@ -882,7 +894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
         <v>32</v>
       </c>
@@ -891,7 +903,7 @@
       <c r="D34" s="12"/>
       <c r="E34" s="10"/>
     </row>
-    <row r="35" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
         <v>33</v>
       </c>
@@ -902,7 +914,7 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
     </row>
-    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
         <v>34</v>
       </c>
@@ -914,7 +926,7 @@
       <c r="AR36" s="14"/>
       <c r="AS36" s="5"/>
     </row>
-    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
         <v>31</v>
       </c>
@@ -927,11 +939,11 @@
       <c r="AR37" s="15"/>
       <c r="AS37" s="16"/>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AR38" s="15"/>
       <c r="AS38" s="16"/>
     </row>
-    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
         <v>35</v>
       </c>
@@ -940,7 +952,7 @@
       <c r="AR39" s="15"/>
       <c r="AS39" s="16"/>
     </row>
-    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
         <v>31</v>
       </c>
@@ -952,14 +964,14 @@
       <c r="AR40" s="15"/>
       <c r="AS40" s="16"/>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10"/>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="AR41" s="15"/>
       <c r="AS41" s="16"/>
     </row>
-    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
         <v>36</v>
       </c>
@@ -976,7 +988,7 @@
       <c r="AR42" s="15"/>
       <c r="AS42" s="16"/>
     </row>
-    <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
         <v>31</v>
       </c>
@@ -1005,7 +1017,7 @@
       <c r="AR43" s="15"/>
       <c r="AS43" s="16"/>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H44" s="6" t="n">
         <v>1</v>
       </c>
@@ -1027,7 +1039,7 @@
       <c r="AR44" s="15"/>
       <c r="AS44" s="16"/>
     </row>
-    <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
         <v>37</v>
       </c>
@@ -1054,7 +1066,7 @@
       <c r="AR45" s="15"/>
       <c r="AS45" s="16"/>
     </row>
-    <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
         <v>31</v>
       </c>
@@ -1083,7 +1095,7 @@
       <c r="AR46" s="15"/>
       <c r="AS46" s="16"/>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H47" s="6" t="n">
         <v>4</v>
       </c>
@@ -1103,7 +1115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
         <v>38</v>
       </c>
@@ -1126,7 +1138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
         <v>31</v>
       </c>
@@ -1153,7 +1165,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H50" s="6" t="n">
         <v>7</v>
       </c>
@@ -1173,7 +1185,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
         <v>39</v>
       </c>
@@ -1196,7 +1208,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
         <v>31</v>
       </c>
@@ -1223,7 +1235,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H53" s="6" t="n">
         <v>10</v>
       </c>
@@ -1243,7 +1255,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
         <v>40</v>
       </c>
@@ -1266,7 +1278,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
         <v>31</v>
       </c>
@@ -1293,7 +1305,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H56" s="6" t="n">
         <v>13</v>
       </c>
@@ -1313,7 +1325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
         <v>41</v>
       </c>
@@ -1336,7 +1348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
         <v>31</v>
       </c>
@@ -1345,35 +1357,35 @@
         <v>0.833</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B61" s="17" t="n">
-        <f aca="false">COUNTIFS(L44:L57, "fair", M44:M57, "yes") / COUNTIF(M44:M57, "yes")</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">COUNTIFS(L44:L57, "excellent", M44:M57, "yes") / COUNTIF(M44:M57, "yes")</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
         <v>31</v>
       </c>
       <c r="B64" s="17" t="n">
-        <f aca="false">ROUND(COUNTIFS(L44:L57, "fair", M44:M57, "no") / COUNTIF(M44:M57, "no"), 3)</f>
-        <v>0.667</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">ROUND(COUNTIFS(L44:L57, "excellent", M44:M57, "no") / COUNTIF(M44:M57, "no"), 3)</f>
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13" t="s">
         <v>44</v>
       </c>
@@ -1384,9 +1396,9 @@
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
     </row>
-    <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -1395,35 +1407,27 @@
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
     </row>
-    <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B71" s="17" t="n">
         <f aca="false">ROUND(B43*B49*B55*B61*(8/14),3)</f>
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B72" s="17" t="n">
         <f aca="false">ROUND(B46*B52*B58*B64*(6/14),3)</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="B75" s="17" t="n">
-        <v>0.06</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1436,8 +1440,14 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="10"/>
+    <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="17" t="n">
+        <f aca="false">B71*(B37/14)</f>
+        <v>0.008</v>
+      </c>
       <c r="H77" s="4" t="s">
         <v>1</v>
       </c>
@@ -1457,7 +1467,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B78" s="17" t="n">
+        <f aca="false">ROUND(B72*(B40/14),3)</f>
+        <v>0.013</v>
+      </c>
       <c r="H78" s="6" t="n">
         <v>1</v>
       </c>
@@ -1477,7 +1494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H79" s="6" t="n">
         <v>2</v>
       </c>
@@ -1497,7 +1514,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H80" s="6" t="n">
         <v>3</v>
       </c>
@@ -1517,7 +1534,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="H81" s="6" t="n">
         <v>4</v>
       </c>
@@ -1537,7 +1557,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B82" s="17" t="n">
+        <f aca="false">MAX(B77:B78)</f>
+        <v>0.013</v>
+      </c>
       <c r="H82" s="6" t="n">
         <v>5</v>
       </c>
@@ -1557,7 +1584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H83" s="6" t="n">
         <v>6</v>
       </c>
@@ -1577,7 +1604,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H84" s="6" t="n">
         <v>7</v>
       </c>
@@ -1597,7 +1624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H85" s="6" t="n">
         <v>8</v>
       </c>
@@ -1617,7 +1644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H86" s="6" t="n">
         <v>9</v>
       </c>
@@ -1637,7 +1664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H87" s="6" t="n">
         <v>10</v>
       </c>
@@ -1657,7 +1684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H88" s="6" t="n">
         <v>11</v>
       </c>
@@ -1677,7 +1704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H89" s="6" t="n">
         <v>12</v>
       </c>
@@ -1697,7 +1724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H90" s="6" t="n">
         <v>13</v>
       </c>
@@ -1717,7 +1744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H91" s="6" t="n">
         <v>14</v>
       </c>

--- a/강아지 입양 여부- 답지.xlsx
+++ b/강아지 입양 여부- 답지.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="52">
   <si>
     <t xml:space="preserve">아래의 표는 각각의 조건이 주어졌을 때 강아지 입양 여부 테이블 입니다. </t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t xml:space="preserve">5. 아래와 같이 X라는 사람의 조건이 주어졌을 때 P(X|강아지 입양 여부 = yes, no)인 확률을 구하시오(위에 확률들 참고해서 작성)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X =(주거지 = 김해, 수입 = medium, 성별 = 남자, 신용등급=fair) </t>
   </si>
   <si>
     <t xml:space="preserve">답  (yes)         :       </t>
@@ -480,7 +477,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AS91"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.5"/>
@@ -1398,7 +1395,7 @@
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -1409,7 +1406,7 @@
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="17" t="n">
         <f aca="false">ROUND(B43*B49*B55*B61*(8/14),3)</f>
@@ -1418,7 +1415,7 @@
     </row>
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" s="17" t="n">
         <f aca="false">ROUND(B46*B52*B58*B64*(6/14),3)</f>
@@ -1427,7 +1424,7 @@
     </row>
     <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1442,7 +1439,7 @@
     </row>
     <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" s="17" t="n">
         <f aca="false">B71*(B37/14)</f>
@@ -1469,7 +1466,7 @@
     </row>
     <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78" s="17" t="n">
         <f aca="false">ROUND(B72*(B40/14),3)</f>
@@ -1536,7 +1533,7 @@
     </row>
     <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="6" t="n">
         <v>4</v>
@@ -1559,7 +1556,7 @@
     </row>
     <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82" s="17" t="n">
         <f aca="false">MAX(B77:B78)</f>
@@ -1781,7 +1778,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1799,7 +1796,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
